--- a/05_Figures/F06_prediction/proteins/T2/comp_hypertrophy/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T2/comp_hypertrophy/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="207">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -137,48 +137,51 @@
     <t xml:space="preserve">HADHA</t>
   </si>
   <si>
+    <t xml:space="preserve">JPT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LMAN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDRG2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEC23A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSFM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHCYL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIMP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENDOD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME1</t>
+  </si>
+  <si>
     <t xml:space="preserve">MLEC</t>
   </si>
   <si>
-    <t xml:space="preserve">ENDOD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LMAN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDRG2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEC23A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSFM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIMP1</t>
+    <t xml:space="preserve">C11orf54</t>
   </si>
   <si>
     <t xml:space="preserve">EIF3G</t>
   </si>
   <si>
+    <t xml:space="preserve">ESYT1</t>
+  </si>
+  <si>
     <t xml:space="preserve">GAA</t>
   </si>
   <si>
-    <t xml:space="preserve">JPT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C11orf54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESYT1</t>
-  </si>
-  <si>
     <t xml:space="preserve">NDUFAB1</t>
   </si>
   <si>
@@ -188,72 +191,72 @@
     <t xml:space="preserve">ARMT1</t>
   </si>
   <si>
+    <t xml:space="preserve">XRCC5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP2A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPS27</t>
+  </si>
+  <si>
     <t xml:space="preserve">OGDH</t>
   </si>
   <si>
+    <t xml:space="preserve">SDHA</t>
+  </si>
+  <si>
     <t xml:space="preserve">SLC25A3</t>
   </si>
   <si>
-    <t xml:space="preserve">XRCC5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP2A3</t>
-  </si>
-  <si>
     <t xml:space="preserve">MRPL22</t>
   </si>
   <si>
     <t xml:space="preserve">NPEPPS</t>
   </si>
   <si>
+    <t xml:space="preserve">RPS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUSP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PABPC4</t>
+  </si>
+  <si>
     <t xml:space="preserve">PAFAH1B3</t>
   </si>
   <si>
-    <t xml:space="preserve">SDHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHCYL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPS27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PABPC4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUSP3</t>
+    <t xml:space="preserve">PHKG1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP2R2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC44A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYNCRIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACNB3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLDIP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QDPR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COQ8A</t>
   </si>
   <si>
     <t xml:space="preserve">IDH2</t>
   </si>
   <si>
-    <t xml:space="preserve">PHKG1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POLDIP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP2R2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QDPR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SYNCRIP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CACNB3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COQ8A</t>
-  </si>
-  <si>
     <t xml:space="preserve">CDC37</t>
   </si>
   <si>
@@ -263,324 +266,345 @@
     <t xml:space="preserve">HRC</t>
   </si>
   <si>
+    <t xml:space="preserve">NUDT16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DENR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDH3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMA7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMD10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TNPO3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAG3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACNA1S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTN4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STK38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKR1C3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSDE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTPS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCTN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNM1L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNLL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPCAT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPK1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFB11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEDD8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRPS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEPTIN6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOMM70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TXN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TXN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WDR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACAD9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACADSB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACAT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACSF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APOO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP1A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5PB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5PD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATXN10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCL2L13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BZW2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAND1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSRP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYB5B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DARS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDAH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDX17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHRS7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF2S3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF5B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESYT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAM114A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FARSB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FITM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GANAB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCSH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLRX5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSTO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIBADH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDH3B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LANCL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LTA4H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LYRM7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP1LC3B2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPL47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIBAN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPEPL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTUB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PBXIP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCCB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDLIM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLIN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP3R1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRKAR2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMD7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAB1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAB8A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBBP4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RMDN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROMO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUVBL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUVBL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S100A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDR39U1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SGTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC16A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPTAN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STIP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STOML2</t>
+  </si>
+  <si>
     <t xml:space="preserve">STT3B</t>
   </si>
   <si>
-    <t xml:space="preserve">DENR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDH3A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMA7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WDR1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAG3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUDT16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGLS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMD10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RTN4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STK38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TNPO3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKR1C3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CACNA1S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSDE1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTPS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FABP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAM114A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPCAT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFB11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRPS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACAD9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACADSB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACAT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACSF2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APOO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5PB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5PD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCL2L13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAND1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CISD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSRP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYB5B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DARS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCTN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDAH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDX17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHRS7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNM1L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNLL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF2S3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESYT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FARSB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FITM2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GANAB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GATD3B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GDI2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSTO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HIBADH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDH3B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDI1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LANCL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LTA4H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LYRM7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP1LC3B2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPK1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEDD8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NIBAN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPEPL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OTUB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PBXIP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCCB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDLIM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PFN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLIN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP3R1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRKAR2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMD7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB1B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB8A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RBBP4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RMDN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROMO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUVBL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUVBL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S100A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SGTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC16A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC44A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPTAN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPTBN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STIP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STOML2</t>
-  </si>
-  <si>
     <t xml:space="preserve">STX7</t>
   </si>
   <si>
@@ -596,16 +620,16 @@
     <t xml:space="preserve">TMEM109</t>
   </si>
   <si>
-    <t xml:space="preserve">TOMM70</t>
+    <t xml:space="preserve">TSPO</t>
   </si>
   <si>
     <t xml:space="preserve">TST</t>
   </si>
   <si>
-    <t xml:space="preserve">TXN2</t>
-  </si>
-  <si>
     <t xml:space="preserve">TXNRD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBE2M</t>
   </si>
   <si>
     <t xml:space="preserve">UCHL1</t>
@@ -998,16 +1022,16 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.30988264815429</v>
+        <v>-1.20702174999401</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.828571428571429</v>
+        <v>-0.8</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -1031,29 +1055,21 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.30988264815429</v>
+        <v>-1.20702174999401</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.828571428571429</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.860696517412935</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.995024875621891</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.642896596842973</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.62210310030916</v>
-      </c>
+        <v>-0.8</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1077,2206 +1093,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.480354104696899</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.15938501937112</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-0.679463067667925</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.512955917560405</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-1.58696253051649</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.284744363341703</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.146385892559185</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.628571984929077</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.782023013656116</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.441755833607847</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.69339790675751</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.0611675271351837</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.336127176312649</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.534542891232524</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.474784030758989</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-0.249158671823408</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-1.14347987515902</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.351336947293944</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.04450407065067</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-1.6608690346354</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-1.78451636387568</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.362359255301384</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-0.437084841132142</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-1.90202974623228</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.0218557196101856</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-1.24862686162018</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-1.0648943396369</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-1.19443955428864</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-0.56008989449867</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-0.0208114089487703</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-1.16094637227043</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-0.130322517534663</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-0.439111736391602</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-0.767824398506473</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.922070117079541</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-0.451328703542528</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-0.824051981114283</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-1.29115833959475</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-1.69422273982189</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-0.444128029974834</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-0.331374503716714</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-2.06312494481559</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0.199318990586271</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-0.742793195085254</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-1.36868370883552</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-2.62634233492709</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.824778162265845</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-0.790816009983327</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-1.36312418028741</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.288253163891945</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-1.45215200791158</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.329192711455995</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.89796329643033</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-0.807834103505355</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-0.397612285000779</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-0.63875623152059</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-0.494627491194657</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-0.439872049259178</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-1.13217553378414</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-1.59699173376318</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-0.740890461676779</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-0.0150426418313137</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>0.0789043057461649</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-1.72369054328733</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-1.98520911391371</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-0.355971018890202</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-0.455391439230086</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>-0.247017014990416</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-0.423677339390489</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-1.65168923861935</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-0.112736119265396</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-0.22436450582609</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-0.513373833829449</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-0.388791397620892</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-0.354285240191828</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>-0.23249837286892</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-0.618088136442911</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-0.280034498089336</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-1.1660561420585</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>0.61002197118252</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>0.10763281170078</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-0.348888970995821</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-0.909904348408677</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-0.306574821007558</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>0.202885579110215</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>0.340488268974453</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-0.0436706087628764</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-0.786331690231212</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-0.515936341603909</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-1.43991351968856</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-0.13120556435036</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-0.786449413960766</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-1.38551559475955</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>0.0239161843508505</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-0.681436018580557</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>0.146105519196275</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-0.313442460281077</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>0.506329688082688</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-0.61412458022465</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-1.71762799961878</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-1.00968192415234</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-2.07644256628063</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-0.52187802317478</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-0.36128093048612</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>0.203396554884225</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-1.1472461471437</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-0.350093426321445</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-0.794981979179747</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-0.918100878277445</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-1.00483308486974</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-0.75203227386907</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-0.0682394074635018</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-1.1579291223108</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-0.409444398887973</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-0.751791712860129</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-1.98947729301162</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>0.468904833525046</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-2.03407595810871</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-1.02619159121985</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-0.684632391900087</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-0.668274893183757</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>-1.66138832833526</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-0.851456731497906</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>-0.518396999143522</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-0.765254390503806</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-0.265184089613978</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-0.663863742158711</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-0.145587819978744</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>0.0284612405046792</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-0.977705529706824</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>0.0737048159868351</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.643738971144905</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-1.72499625440143</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-0.799723061945437</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-0.976951268571926</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-1.10932057086424</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-0.154326467325252</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-1.10764572612734</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-0.656929574605294</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-0.991988934144242</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>0.00103334938331645</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-0.393362638768426</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>0.0790961011081965</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-0.48195891692974</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-1.05162822703195</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-1.19546070261348</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-0.171174096400303</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-0.260234099573487</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-2.68723023409523</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>0.304125734371073</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-0.943643168762873</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>0.375326694507644</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-0.723164180925777</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-0.515057861722881</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-0.806315240604054</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>0.314432519193862</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-0.674136976168291</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-1.08447491240957</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-0.881566962706055</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-0.766229814217238</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>-0.589069938080316</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>0.192919828097832</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.531439460937271</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-0.688684503873704</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-1.3377023409348</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-1.81636986070785</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-0.185456216067881</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>0.638433878771071</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>0.362513021583465</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-0.309081103683906</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-0.191003228258525</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-0.447046315326138</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>-1.19918058866388</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-0.590777035906454</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-1.43935152620315</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-0.586081668960411</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>-1.21059497710018</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-0.510961353616465</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>-0.133598991741647</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>-0.705286701810029</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-0.226119049574348</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-0.860952440275663</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-0.64134313142897</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>0.181457727053271</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>0.391872285707586</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-0.992863653811113</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-2.02376392153829</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>0.289933596332024</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>-0.36547207079876</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>-0.299906569562475</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-0.332397587347165</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-0.165756746781204</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>0.0349997641333646</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>-0.790964411562053</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-0.473045206083744</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-0.762759444996603</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-0.31989434476691</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-0.805357018864707</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-1.37157813350803</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-1.23736011218615</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3319,7 +1135,7 @@
         <v>9.43</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5951136908694</v>
+        <v>7.4488998292686</v>
       </c>
     </row>
     <row r="3">
@@ -3336,7 +1152,7 @@
         <v>20.73</v>
       </c>
       <c r="E3" t="n">
-        <v>-6.55695320745891</v>
+        <v>-7.07539002198571</v>
       </c>
     </row>
     <row r="4">
@@ -3353,7 +1169,7 @@
         <v>13.69</v>
       </c>
       <c r="E4" t="n">
-        <v>5.64496693079438</v>
+        <v>5.75836189916502</v>
       </c>
     </row>
     <row r="5">
@@ -3370,7 +1186,7 @@
         <v>10.45</v>
       </c>
       <c r="E5" t="n">
-        <v>2.71525676051063</v>
+        <v>2.70987650120433</v>
       </c>
     </row>
     <row r="6">
@@ -3387,7 +1203,7 @@
         <v>14.93</v>
       </c>
       <c r="E6" t="n">
-        <v>-5.4503841581553</v>
+        <v>-0.419251478813814</v>
       </c>
     </row>
     <row r="7">
@@ -3404,7 +1220,7 @@
         <v>13.79</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3878544684597</v>
+        <v>-0.953954276114248</v>
       </c>
     </row>
     <row r="8">
@@ -3421,7 +1237,7 @@
         <v>8.06</v>
       </c>
       <c r="E8" t="n">
-        <v>5.60662158540633</v>
+        <v>5.47552656560502</v>
       </c>
     </row>
     <row r="9">
@@ -3438,7 +1254,7 @@
         <v>0.79</v>
       </c>
       <c r="E9" t="n">
-        <v>4.62097195862401</v>
+        <v>4.19379339220923</v>
       </c>
     </row>
     <row r="10">
@@ -3455,7 +1271,7 @@
         <v>0.85</v>
       </c>
       <c r="E10" t="n">
-        <v>5.94526693500666</v>
+        <v>5.80795924411377</v>
       </c>
     </row>
     <row r="11">
@@ -3472,7 +1288,7 @@
         <v>-4.09</v>
       </c>
       <c r="E11" t="n">
-        <v>6.48496443524824</v>
+        <v>6.6833534275919</v>
       </c>
     </row>
     <row r="12">
@@ -3489,7 +1305,7 @@
         <v>-0.74</v>
       </c>
       <c r="E12" t="n">
-        <v>8.70839268416545</v>
+        <v>9.29291965268957</v>
       </c>
     </row>
     <row r="13">
@@ -3506,7 +1322,7 @@
         <v>-1.86</v>
       </c>
       <c r="E13" t="n">
-        <v>12.9655521947926</v>
+        <v>12.525415220619</v>
       </c>
     </row>
     <row r="14">
@@ -3523,7 +1339,7 @@
         <v>-6.6</v>
       </c>
       <c r="E14" t="n">
-        <v>8.99579921330685</v>
+        <v>8.92427369064691</v>
       </c>
     </row>
     <row r="15">
@@ -3540,7 +1356,7 @@
         <v>-5.99</v>
       </c>
       <c r="E15" t="n">
-        <v>8.78328403070693</v>
+        <v>8.50475322606397</v>
       </c>
     </row>
     <row r="16">
@@ -3557,7 +1373,7 @@
         <v>-0.48</v>
       </c>
       <c r="E16" t="n">
-        <v>5.17695577204465</v>
+        <v>4.54271234422722</v>
       </c>
     </row>
   </sheetData>
@@ -3650,10 +1466,10 @@
         <v>41</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -3667,10 +1483,10 @@
         <v>42</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -3684,10 +1500,10 @@
         <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -3701,10 +1517,10 @@
         <v>44</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -3752,10 +1568,10 @@
         <v>47</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="12">
@@ -3769,10 +1585,10 @@
         <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="13">
@@ -3786,10 +1602,10 @@
         <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -3803,10 +1619,10 @@
         <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="15">
@@ -3837,10 +1653,10 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="17">
@@ -3854,10 +1670,10 @@
         <v>53</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="18">
@@ -3871,10 +1687,10 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="19">
@@ -3888,10 +1704,10 @@
         <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>0.666666666666667</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="20">
@@ -3905,10 +1721,10 @@
         <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E20" t="n">
-        <v>0.666666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="21">
@@ -3922,10 +1738,10 @@
         <v>57</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>0.666666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="22">
@@ -3939,10 +1755,10 @@
         <v>58</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
-        <v>0.666666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="23">
@@ -3973,10 +1789,10 @@
         <v>60</v>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="25">
@@ -3990,10 +1806,10 @@
         <v>61</v>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="26">
@@ -4007,10 +1823,10 @@
         <v>62</v>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="27">
@@ -4024,10 +1840,10 @@
         <v>63</v>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="28">
@@ -4058,10 +1874,10 @@
         <v>65</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>0.533333333333333</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="30">
@@ -4075,10 +1891,10 @@
         <v>66</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>0.533333333333333</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="31">
@@ -4126,10 +1942,10 @@
         <v>69</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>0.466666666666667</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="34">
@@ -4143,10 +1959,10 @@
         <v>70</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E34" t="n">
-        <v>0.466666666666667</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="35">
@@ -4160,10 +1976,10 @@
         <v>71</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E35" t="n">
-        <v>0.466666666666667</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="36">
@@ -4177,10 +1993,10 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E36" t="n">
-        <v>0.466666666666667</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="37">
@@ -4194,10 +2010,10 @@
         <v>73</v>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E37" t="n">
-        <v>0.466666666666667</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="38">
@@ -4262,10 +2078,10 @@
         <v>77</v>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="42">
@@ -4296,10 +2112,10 @@
         <v>79</v>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>0.333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="44">
@@ -4364,10 +2180,10 @@
         <v>83</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E47" t="n">
-        <v>0.266666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="48">
@@ -4449,10 +2265,10 @@
         <v>88</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E52" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="53">
@@ -4466,10 +2282,10 @@
         <v>89</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E53" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="54">
@@ -4823,10 +2639,10 @@
         <v>110</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="75">
@@ -4840,10 +2656,10 @@
         <v>111</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="76">
@@ -4857,10 +2673,10 @@
         <v>112</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="77">
@@ -4874,10 +2690,10 @@
         <v>113</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="78">
@@ -4891,10 +2707,10 @@
         <v>114</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="79">
@@ -6322,6 +4138,142 @@
         <v>1</v>
       </c>
       <c r="E162" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="s">
+        <v>199</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="s">
+        <v>200</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="s">
+        <v>201</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="s">
+        <v>202</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="s">
+        <v>203</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="s">
+        <v>204</v>
+      </c>
+      <c r="D168" t="n">
+        <v>1</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="s">
+        <v>205</v>
+      </c>
+      <c r="D169" t="n">
+        <v>1</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="s">
+        <v>206</v>
+      </c>
+      <c r="D170" t="n">
+        <v>1</v>
+      </c>
+      <c r="E170" t="n">
         <v>0.0666666666666667</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/T2/comp_hypertrophy/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T2/comp_hypertrophy/spls/c_data/results.xlsx
@@ -1058,7 +1058,7 @@
         <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-1.20702174999401</v>
@@ -1066,10 +1066,18 @@
       <c r="I3" t="n">
         <v>-0.8</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.835820895522388</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.990049751243781</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.637205387137711</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.615193199455453</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1093,6 +1101,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.5205868942979</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.172632508654794</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.761617051660324</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.291634954757465</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-1.54450735246345</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.410312261050917</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.137242656629225</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.780342622785332</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.765629937359542</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.354527204685414</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.800222302796275</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.0350387325003079</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.386816372568418</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.41287761906148</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.669790344126264</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.232849449296165</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.819936089743209</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.295031820965385</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.110815857224207</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1.71924881245663</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-2.43044634398571</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.383174946105187</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.055851938987255</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-1.56928277079287</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.162657379061454</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-1.34085305670681</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-1.03156616331367</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-1.30175512079619</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.856648275064964</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.141063076190357</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-1.28678682696105</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.0288871111880975</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.560448573383223</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.584447031700044</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-1.09618661466129</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.340160400988992</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-1.15029049007839</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-1.15525161433496</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-1.42958134392296</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.437243508931814</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.157146372482313</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-2.02384506502262</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.209952207082972</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.737732069305342</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-1.37462869769136</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-1.41304248794138</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.813839785332445</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-1.06190637923551</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-1.38607614645792</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.376820957109777</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-1.6233810223161</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.40793544430224</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.701789202331617</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.83183697895565</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.434889157657927</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-0.362332367287218</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-0.521723982157108</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.358658916410054</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-1.05426896033626</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-1.62677922930552</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-1.34465993140687</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.0437053061236242</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.21928283489587</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-1.69402708300568</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-2.10264274153661</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.433299205136145</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.415195091477251</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.212075357872718</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.295103278272911</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-1.72400596841337</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.0989389997790571</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.200541031603196</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-0.416080956994152</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.0740268461704998</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-0.0916428950357053</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-0.252744980694235</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.746858702836013</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.551726764535336</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.952285646771238</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.570339844577332</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0.161816552258723</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.318835944974151</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.945198888180399</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.373340412756344</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.193568834430126</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.428288589683424</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0.00640532767761348</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.713687862892036</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-0.485798275124512</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-1.35957947802539</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-0.127386201119394</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.891216923289728</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-1.44186989647798</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.083409451437896</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-0.453161371942143</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.186861421544971</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-0.20985429504806</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.42927616315887</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-1.13659045840985</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-1.83759543867629</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-1.04327287992687</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-1.95791984658587</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.486031938778017</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-0.390222653237924</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0.251659075119335</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-1.18443508161883</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-0.288647507993356</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.300172305226695</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-0.932816859794069</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-1.01050657001363</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-0.720338289700567</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.300930644597178</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-1.10549869115323</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-0.650639242938883</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-0.857518124372407</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-1.7456500033135</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.466171927539962</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-1.69690505492165</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-1.05224755179406</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.723910549275878</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.700830927514126</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-1.30813184869859</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-0.640475517351263</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.542019945566724</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.682014529090511</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-0.270806043491913</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.624673563965501</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.100390616115895</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.035284480259358</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-0.830114740390064</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.0533135794146224</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.58272084335667</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-1.83841253826782</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-1.3440547423538</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-1.23725742686345</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-1.09796514311159</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-0.207484292511586</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.845159019269326</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-1.01695835713377</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-0.701732741688488</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.0112113229423458</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-0.43581388421859</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0.280659689201052</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.49052972556247</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-1.07312068400129</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-1.0055418642215</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-0.141859601399074</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-0.344174691012733</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-2.78563485569164</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0.09224138103884</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-0.729723587231805</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0.400000935246106</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-0.725153260387545</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.525266166291998</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-0.781325616328696</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0.545464151977531</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-0.611593629987304</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-1.14343656196805</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.772557438003271</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-1.04357206564547</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-1.00919673205951</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0.434107221965013</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.546827059328171</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-0.697818258656421</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-1.51217616921252</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-1.08026652950505</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.174178227198744</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>0.832228018715512</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>0.277611053906942</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.285759150537625</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-0.164456453555165</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-0.517946928769504</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-1.09862323465369</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.822305570505913</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-1.04367895674105</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-0.595464757524619</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-1.42924200560103</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-0.391791106363725</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-0.087569390589223</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-0.784576585899907</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-0.315635045328163</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-0.867323063695196</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-0.660390142405946</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0.246807625834269</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0.390765246113486</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-0.964092971472989</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-1.75639606112349</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-0.249328851606357</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-0.292329191254511</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-0.284807506284175</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.340941696775798</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-0.218307658789611</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-0.00472835636052649</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-0.676085571338365</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-0.471343045637082</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-0.721395945625513</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.409016540607105</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-0.738387848466586</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-1.7630004028995</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-1.19151396277756</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
